--- a/src/ergodic_search/scripts/ergodic_metric.xlsx
+++ b/src/ergodic_search/scripts/ergodic_metric.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.2834375863836294</t>
+          <t>0.22076733975331214</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.013620720232904646</t>
+          <t>0.002509392767156106</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.22076733975331214</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.002509392767156106</t>
         </is>
       </c>
     </row>

--- a/src/ergodic_search/scripts/ergodic_metric.xlsx
+++ b/src/ergodic_search/scripts/ergodic_metric.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,227 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.18973502494053224</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0015363019238126415</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.31628346677345387</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.31628346677345387</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.31628346677345387</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.09362820354314119</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.1357151219706464</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.006629297200571728</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.24524008125282326</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05771711181597938</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.5596583419469264</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.5596583419469264</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.1505268939755275</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.26172304025067095</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.02261664580086309</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.26172304025067095</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.02261664580086309</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/ergodic_search/scripts/ergodic_metric.xlsx
+++ b/src/ergodic_search/scripts/ergodic_metric.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,57 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>baseline1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.4486248406874438</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.026608809478039324</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>baseline1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.4950937452019154</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.1053032904859674</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>my_strategy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.19757477596312764</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.00964890562111088</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
